--- a/data/entrada/docencia/estudios.xlsx
+++ b/data/entrada/docencia/estudios.xlsx
@@ -6,7 +6,8 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Datos" r:id="rId3" sheetId="1"/>
+    <sheet name="Export Worksheet" r:id="rId3" sheetId="1"/>
+    <sheet name="SQL" r:id="rId4" sheetId="2"/>
   </sheets>
 </workbook>
 </file>
@@ -67,7 +68,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B130"/>
+  <sheetPr>
+    <pageSetUpPr fitToPage="true"/>
+  </sheetPr>
+  <dimension ref="A1:C285"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -81,25 +85,36 @@
           <t>nombre</t>
         </is>
       </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>servicio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>90001.0</v>
+        <v>90030.0</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Grado en Administración y Dirección de Empresas</t>
-        </is>
+          <t>Grau en Relacions Laborals i Recursos Humans</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>90002.0</v>
+        <v>90032.0</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Grado en Arquitectura Técnica</t>
-        </is>
+          <t>Grau en Turisme</t>
+        </is>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="4">
@@ -108,928 +123,1207 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Grado en Comunicación Audiovisual</t>
-        </is>
+          <t>Grau en Comunicació Audiovisual</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>90004.0</v>
+        <v>90026.0</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Grado en Criminología y Seguridad</t>
-        </is>
+          <t>Grau en Periodisme</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>90005.0</v>
+        <v>90016.0</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Grado en Diseño y Desarrollo de Videojuegos</t>
-        </is>
+          <t>Grau en Estudis Anglesos</t>
+        </is>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>90006.0</v>
+        <v>90028.0</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Grado en Derecho</t>
-        </is>
+          <t>Grau en Publicitat i Relacions Públiques</t>
+        </is>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>90007.0</v>
+        <v>90031.0</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Grado en Economía</t>
-        </is>
+          <t>Grau en Traducció i Interpretació</t>
+        </is>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>90008.0</v>
+        <v>90029.0</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Grado en Ingeniería Agroalimentaria y del Medio Rural</t>
-        </is>
+          <t>Grau en Química</t>
+        </is>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>90009.0</v>
+        <v>90002.0</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Grado en Ingeniería Eléctrica para la Transición Energética</t>
-        </is>
+          <t>Grau en Arquitectura Tècnica</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>90010.0</v>
+        <v>90001.0</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Grado en Ingeniería en Diseño Industrial y Desarrollo de Productos</t>
-        </is>
+          <t>Grau en Administració d'Empreses</t>
+        </is>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>90011.0</v>
+        <v>90007.0</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Grado en Ingeniería en Tecnologías Industriales</t>
-        </is>
+          <t>Grau en Economia</t>
+        </is>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>90012.0</v>
+        <v>90017.0</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Grado en Ingeniería Informática</t>
-        </is>
+          <t>Grau en Finances i Comptabilitat</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>90013.0</v>
+        <v>90006.0</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Grado en Ingeniería Mecánica</t>
-        </is>
+          <t>Grau en Dret</t>
+        </is>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>90014.0</v>
+        <v>90004.0</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Grado en Ingeniería Química</t>
-        </is>
+          <t>Grau en Criminologia i Seguretat</t>
+        </is>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>90016.0</v>
+        <v>90019.0</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Grado en Estudios Ingleses / Bachelor's Degree in English Studies</t>
-        </is>
+          <t>Grau en Història i Patrimoni</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>90017.0</v>
+        <v>90020.0</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Grado en Finanzas y Contabilidad</t>
-        </is>
+          <t>Grau en Humanitats: Estudis Interculturals</t>
+        </is>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>90018.0</v>
+        <v>90024.0</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Grado en Gestión y Administración Pública</t>
-        </is>
+          <t>Grau en Mestre o Mestra d'Educació Infantil</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>90019.0</v>
+        <v>90025.0</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Grado en Historia y Patrimonio</t>
-        </is>
+          <t>Grau en Mestre o Mestra d'Educació Primària</t>
+        </is>
+      </c>
+      <c r="C19" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>90020.0</v>
+        <v>90027.0</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Grado en Humanidades</t>
-        </is>
+          <t>Grau en Psicologia</t>
+        </is>
+      </c>
+      <c r="C20" s="1" t="n">
+        <v>2922.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>90021.0</v>
+        <v>90014.0</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Grado en Enfermería</t>
-        </is>
+          <t>Grau en Enginyeria Química</t>
+        </is>
+      </c>
+      <c r="C21" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>90022.0</v>
+        <v>90011.0</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Grado en Matemática Computacional</t>
-        </is>
+          <t>Grau en Enginyeria en Tecnologies Industrials</t>
+        </is>
+      </c>
+      <c r="C22" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>90023.0</v>
+        <v>90013.0</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Grado en Medicina</t>
-        </is>
+          <t>Grau en Enginyeria Mecànica</t>
+        </is>
+      </c>
+      <c r="C23" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>90024.0</v>
+        <v>90022.0</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Grado en Maestro o Maestra en Educación Infantil</t>
-        </is>
+          <t>Grau en Matemàtica Computacional</t>
+        </is>
+      </c>
+      <c r="C24" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>90025.0</v>
+        <v>90010.0</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Grado en Maestro o Maestra de Educación Primaria</t>
-        </is>
+          <t>Grau en Enginyeria en Disseny Industrial i Desenvolupament de Productes</t>
+        </is>
+      </c>
+      <c r="C25" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>90026.0</v>
+        <v>90012.0</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Grado en Periodismo</t>
-        </is>
+          <t>Grau en Enginyeria Informàtica</t>
+        </is>
+      </c>
+      <c r="C26" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>90027.0</v>
+        <v>90008.0</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grado en Psicología</t>
-        </is>
+          <t>Grau en Enginyeria Agroalimentària i del Medi Rural</t>
+        </is>
+      </c>
+      <c r="C27" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>90028.0</v>
+        <v>90009.0</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grado en Publicidad y Comunicación Corporativa</t>
-        </is>
+          <t>Grau en Enginyeria Elèctrica</t>
+        </is>
+      </c>
+      <c r="C28" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>90029.0</v>
+        <v>90023.0</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Grado en Química</t>
-        </is>
+          <t>Grau en Medicina</t>
+        </is>
+      </c>
+      <c r="C29" s="1" t="n">
+        <v>2922.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>90030.0</v>
+        <v>90021.0</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Grado en Relaciones Laborales y Recursos Humanos</t>
-        </is>
+          <t>Grau en Infermeria</t>
+        </is>
+      </c>
+      <c r="C30" s="1" t="n">
+        <v>2922.0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>90031.0</v>
+        <v>90005.0</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Grado en Traducción e Interpretación</t>
-        </is>
+          <t>Grau en Disseny i Desenvolupament de Videojocs</t>
+        </is>
+      </c>
+      <c r="C31" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>90032.0</v>
+        <v>90018.0</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Grado en Turismo</t>
-        </is>
+          <t>Grau en Gestió i Administració Pública</t>
+        </is>
+      </c>
+      <c r="C32" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>90101.0</v>
+        <v>90019.0</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Máster Universitario en Abogacía y Procura</t>
-        </is>
+          <t>Grau en Història i Patrimoni (Pla de 2015)</t>
+        </is>
+      </c>
+      <c r="C33" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>90102.0</v>
+        <v>90020.0</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Máster en Asesoramiento Lingüístico y Cultura Literaria: Aplicaciones al Contexto Valenciano</t>
-        </is>
+          <t>Grau en Humanitats: Estudis Interculturals (Pla de 2015)</t>
+        </is>
+      </c>
+      <c r="C34" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>90103.0</v>
+        <v>90023.0</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Máster Universitario en Biología Molecular, Celular y Genética</t>
-        </is>
+          <t>Grau en Medicina (Pla de 2017)</t>
+        </is>
+      </c>
+      <c r="C35" s="1" t="n">
+        <v>2922.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>90104.0</v>
+        <v>90161.0</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Máster Universitario en Catálisis Homogénea</t>
-        </is>
+          <t>Doble Grau en Administració d'Empreses i Dret</t>
+        </is>
+      </c>
+      <c r="C36" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>90106.0</v>
+        <v>90025.0</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Máster Universitario en Ciencia, Tecnología y Aplicaciones de los Materiales Cerámicos</t>
-        </is>
+          <t>Grau en Mestre o Mestra en Educació Primària (Pla de 2018)</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>90107.0</v>
+        <v>90024.0</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Máster Universitario en Ciencias de la Enfermería</t>
-        </is>
+          <t>Grau en Mestre o Mestra en Educació Infantil (Pla de 2018)</t>
+        </is>
+      </c>
+      <c r="C38" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>90108.0</v>
+        <v>90008.0</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Máster Universitario en Comunicación Intercultural y Enseñanza de Lenguas</t>
-        </is>
+          <t>Grau en Enginyeria Agroalimentària i del Medi Rural (Pla de 2018)</t>
+        </is>
+      </c>
+      <c r="C39" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>90109.0</v>
+        <v>90188.0</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Máster Universitario en Cooperación al Desarrollo</t>
-        </is>
+          <t>Grau en Ciències de l'Activitat Física i de l'Esport</t>
+        </is>
+      </c>
+      <c r="C40" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>90110.0</v>
+        <v>90002.0</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Master Universitario en Didáctica de la Música</t>
-        </is>
+          <t>Grau en Arquitectura Tècnica (Pla de 2020)</t>
+        </is>
+      </c>
+      <c r="C41" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>90111.0</v>
+        <v>90010.0</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Máster Universitario en Dirección de Empresas / Master in Management</t>
-        </is>
+          <t>Grau en Enginyeria en Disseny Industrial i Desenvolupament de Productes (Pla de 2020)</t>
+        </is>
+      </c>
+      <c r="C42" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>90112.0</v>
+        <v>90004.0</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Máster Universitario en Diseño y Fabricación</t>
-        </is>
+          <t>Grau en Criminologia i Seguretat (Pla de 2020)</t>
+        </is>
+      </c>
+      <c r="C43" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>90113.0</v>
+        <v>90190.0</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Máster Universitario en Economía / Master in Economics</t>
-        </is>
+          <t>Grau en Intel·ligència Robòtica</t>
+        </is>
+      </c>
+      <c r="C44" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>90114.0</v>
+        <v>90192.0</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Máster Universitario en Eficiencia Energética y Sostenibilidad</t>
-        </is>
+          <t>Grau en Bioquímica i Biologia Molecular</t>
+        </is>
+      </c>
+      <c r="C45" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>90115.0</v>
+        <v>90032.0</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Máster Universitario en Ingeniería Industrial</t>
-        </is>
+          <t>Grau en Turisme (Pla de 2023)</t>
+        </is>
+      </c>
+      <c r="C46" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>90116.0</v>
+        <v>90019.0</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Máster Universitario en Enseñanza y Adquisición de la Lengua Inglesa en Contextos Multilingües</t>
-        </is>
+          <t>Grau en Història i Patrimoni (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C47" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>90117.0</v>
+        <v>90020.0</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Máster Universitario en Estudios Contemporáneos e Investigación Avanzada</t>
-        </is>
+          <t>Grau en Humanitats (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C48" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>90118.0</v>
+        <v>90001.0</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Máster Universitario en Estudios Internacionales de Paz, Conflictos y Desarrollo</t>
-        </is>
+          <t>Grau en Administració i Direcció d'Empreses (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C49" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>90119.0</v>
+        <v>90007.0</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Máster Universitario en Ética y Democracia</t>
-        </is>
+          <t>Grau en Economia (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C50" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>90120.0</v>
+        <v>90017.0</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Máster Universitario en Física Aplicada</t>
-        </is>
+          <t>Grau en Finances i Comptabilitat (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C51" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>90122.0</v>
+        <v>90193.0</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Máster Universitario en Gestión de la Calidad</t>
-        </is>
+          <t>Grau en Màrqueting</t>
+        </is>
+      </c>
+      <c r="C52" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>90123.0</v>
+        <v>90006.0</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Máster Universitario en Gestión Financiera y Contabilidad Avanzada</t>
-        </is>
+          <t>Grau en Dret (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C53" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>90124.0</v>
+        <v>90161.0</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Máster Universitario en Gestión y Promoción del Desarrollo Local</t>
-        </is>
+          <t>Doble Grau en Administració i Direcció d'Empreses i Dret (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C54" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>90125.0</v>
+        <v>90005.0</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Máster Universitario en Historia del Arte y Cultura Visual</t>
-        </is>
+          <t>Grau en Disseny i Desenvolupament de Videojocs (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C55" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>90126.0</v>
+        <v>90194.0</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Máster Universitario en Historia e Identidades Hispánicas en el Mediterráneo Occidental (siglos XV-XIX)</t>
-        </is>
+          <t>Grau en Economia de l'Empresa Internacional / Bachelor in International Business Economics</t>
+        </is>
+      </c>
+      <c r="C56" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>90127.0</v>
+        <v>90026.0</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Máster Universitario en Igualdad y Género en el Ámbito Público y Privado</t>
-        </is>
+          <t>Grau en Periodisme (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C57" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>90128.0</v>
+        <v>90003.0</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Máster Universitario en Internacionalización Económica: Integración y Comercio Internacional</t>
-        </is>
+          <t>Grau en Comunicació Audiovisual (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C58" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>90129.0</v>
+        <v>90028.0</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Máster Universitario en Intervención y Mediación Familiar</t>
-        </is>
+          <t>Grau en Publicitat i Comunicació Corporativa (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C59" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>90130.0</v>
+        <v>90029.0</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Máster Universitario en Investigación Aplicada en Estudios Feministas, de Género y Ciudadanía</t>
-        </is>
+          <t>Grau en Química (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C60" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>90131.0</v>
+        <v>90196.0</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Máster Universitario en Investigación en Atención Primaria</t>
-        </is>
+          <t>Doble Grau en Mestre o Mestra en Educació Infantil i Primària</t>
+        </is>
+      </c>
+      <c r="C61" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>90132.0</v>
+        <v>90016.0</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Máster Universitario en Investigación en Cerebro y Conducta</t>
-        </is>
+          <t>Grau en Estudis Anglesos / Bachelor in English Studies (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C62" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>90133.0</v>
+        <v>90031.0</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Máster Universitario en Investigación en Traducción e Interpretación</t>
-        </is>
+          <t>Grau en Traducció i Interpretació (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C63" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>90134.0</v>
+        <v>90018.0</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Máster Universitario en Investigación y Biotecnología Agrarias</t>
-        </is>
+          <t>Grau en Gestió i Administració Pública (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C64" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>90135.0</v>
+        <v>90030.0</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Máster Universitario en Lengua Inglesa para el Comercio Internacional / Master in English Language for International Trade</t>
-        </is>
+          <t>Grau en Relacions Laborals i Recursos Humans (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C65" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>90136.0</v>
+        <v>90004.0</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Máster Universitario en Marketing e Investigación de Mercados</t>
-        </is>
+          <t>Grau en Criminologia i Seguretat (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C66" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>90137.0</v>
+        <v>90027.0</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Máster Universitario en Matemática Computacional</t>
-        </is>
+          <t>Grau en Psicologia (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C67" s="1" t="n">
+        <v>2922.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>90138.0</v>
+        <v>90012.0</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Máster Universitario en Nanociencia y Nanotecnología Molecular</t>
-        </is>
+          <t>Grau en Enginyeria Informàtica (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C68" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>90139.0</v>
+        <v>90022.0</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Máster Universitario en Innovación en Comunicación</t>
-        </is>
+          <t>Grau en Matemàtica Computacional (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C69" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>90140.0</v>
+        <v>90198.0</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Máster Universitario en Práctica Jurídica</t>
-        </is>
+          <t>Doble Grau en Disseny i Desenvolupament de Videojocs i Comunicació Audiovisual</t>
+        </is>
+      </c>
+      <c r="C70" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>90141.0</v>
+        <v>90199.0</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Máster Universitario en Prevención de Riesgos Laborales</t>
-        </is>
+          <t>Doble Grau en Comunicació Audiovisual i Humanitats</t>
+        </is>
+      </c>
+      <c r="C71" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>90142.0</v>
+        <v>90009.0</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Máster Universitario en Procura (pendiente de autorización de implantación)</t>
-        </is>
+          <t>Grau en Enginyeria Elèctrica per a la Transició Energètica  (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C72" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>90143.0</v>
+        <v>90013.0</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Máster Universitario en Profesor/a de Educación Secundaria Obligatoria y Bachillerato, Formación Profesional y Enseñanzas de Idiomas</t>
-        </is>
+          <t>Grau en Enginyeria Mecànica (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C73" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>90144.0</v>
+        <v>90014.0</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Máster Universitario en Protección Integrada de Cultivos</t>
-        </is>
+          <t>Grau en Enginyeria Química (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C74" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>90145.0</v>
+        <v>90011.0</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Máster Universitario en Psicología del Trabajo, de las Organizaciones y en Recursos Humanos</t>
-        </is>
+          <t>Grau en Enginyeria en Tecnologies Industrials (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C75" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>90146.0</v>
+        <v>90002.0</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Máster Universitario en Psicología General Sanitaria</t>
-        </is>
+          <t>Grau en Enginyeria de l'Edificació</t>
+        </is>
+      </c>
+      <c r="C76" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>90147.0</v>
+        <v>90176.0</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Máster Universitario en Psicopatología, Salud y Neuropsicología</t>
-        </is>
+          <t>Programa de Doctorat en Informàtica</t>
+        </is>
+      </c>
+      <c r="C77" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>90148.0</v>
+        <v>90169.0</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Máster Universitario en Psicopedagogía</t>
-        </is>
+          <t>Programa de Doctorat en Economia i Empresa</t>
+        </is>
+      </c>
+      <c r="C78" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>90149.0</v>
+        <v>90165.0</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Máster Universitario en Química Aplicada y Farmacológica</t>
-        </is>
+          <t>Programa de Doctorat en Ciències de la Infermeria</t>
+        </is>
+      </c>
+      <c r="C79" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>90150.0</v>
+        <v>90162.0</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Máster Universitario en Química Sostenible</t>
-        </is>
+          <t>Programa de Doctorat en Ciències</t>
+        </is>
+      </c>
+      <c r="C80" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>90151.0</v>
+        <v>90175.0</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Máster Universitario en Química Teórica y Modelización Computacional</t>
-        </is>
+          <t>Programa de Doctorat en Història i Estudis Contemporanis</t>
+        </is>
+      </c>
+      <c r="C81" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>90152.0</v>
+        <v>90172.0</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Máster Universitario en Rehabilitación Psicosocial en Salud Mental Comunitaria</t>
-        </is>
+          <t>Programa de Doctorat en Estudis Internacionals en Pau, Conflictes i Desenvolupament</t>
+        </is>
+      </c>
+      <c r="C82" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>90153.0</v>
+        <v>90183.0</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Máster Universitario Erasmus Mundus en Robótica Avanzada</t>
-        </is>
+          <t>Programa de Doctorat en Tecnologies Industrials i Materials</t>
+        </is>
+      </c>
+      <c r="C83" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>90154.0</v>
+        <v>90168.0</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Máster Universitario en Sistema de Justicia Penal</t>
-        </is>
+          <t>Programa de Doctorat en Dret</t>
+        </is>
+      </c>
+      <c r="C84" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>90155.0</v>
+        <v>90180.0</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Máster Universitario en Sistemas Inteligentes</t>
-        </is>
+          <t>Programa de Doctorat en Psicologia</t>
+        </is>
+      </c>
+      <c r="C85" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>90156.0</v>
+        <v>90177.0</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Máster Universitario en Sostenibilidad y Responsabilidad Social Corporativa</t>
-        </is>
+          <t>Programa de Doctorat en Llengües Aplicades, Literatura i Traducció</t>
+        </is>
+      </c>
+      <c r="C86" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>90157.0</v>
+        <v>90164.0</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Máster Universitario en Técnicas Cromatográficas Aplicadas</t>
-        </is>
+          <t>Programa de Doctorat en Ciències de la Comunicació</t>
+        </is>
+      </c>
+      <c r="C87" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>90158.0</v>
+        <v>90163.0</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Máster Universitario Erasmus Mundus en Tecnología Geoespacial</t>
-        </is>
+          <t>Programa de Doctorat en Ciències Biomèdiques i Salut</t>
+        </is>
+      </c>
+      <c r="C88" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>90159.0</v>
+        <v>90170.0</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Máster Universitario en Tecnologías de la Traducción y Localización</t>
-        </is>
+          <t>Programa de Doctorat en Educació</t>
+        </is>
+      </c>
+      <c r="C89" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>90160.0</v>
+        <v>90181.0</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Máster Universitario en Traducción Médico-Sanitaria</t>
-        </is>
+          <t>Programa de Doctorat en Química Sostenible</t>
+        </is>
+      </c>
+      <c r="C90" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>90161.0</v>
+        <v>90166.0</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Doble Grado en Administración y Dirección de Empresas y Derecho</t>
-        </is>
+          <t>Programa de Doctorat en Desenvolupament Local i Cooperació Internacional</t>
+        </is>
+      </c>
+      <c r="C91" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>90162.0</v>
+        <v>90171.0</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Ciencias</t>
-        </is>
+          <t>Programa de Doctorat en Estudis Interdisciplinars de Gènere</t>
+        </is>
+      </c>
+      <c r="C92" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>90163.0</v>
+        <v>90173.0</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Ciencias Biomédicas y Salud</t>
-        </is>
+          <t>Programa de Doctorat en Ètica i Democràcia</t>
+        </is>
+      </c>
+      <c r="C93" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>90164.0</v>
+        <v>90174.0</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Ciencias de la Comunicación</t>
-        </is>
+          <t>Programa de Doctorat en Història de l'Art</t>
+        </is>
+      </c>
+      <c r="C94" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>90165.0</v>
+        <v>90178.0</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Ciencias de la Enfermería</t>
-        </is>
+          <t>Programa de Doctorat en Marketing</t>
+        </is>
+      </c>
+      <c r="C95" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>90166.0</v>
+        <v>90179.0</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Desarrollo Local y Cooperación Internacional</t>
-        </is>
+          <t>Programa de Doctorat en Nanociència i Nanotecnologia</t>
+        </is>
+      </c>
+      <c r="C96" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="97">
@@ -1038,337 +1332,2476 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Programa de Doctorat en Diseño, Gestión y Evaluación de Políticas Públicas de Bienestar Social</t>
-        </is>
+          <t>Programa de Doctorat en Diseny, Gestió i Avaluació de Polítiques Públiques de Benestar Social</t>
+        </is>
+      </c>
+      <c r="C97" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>90168.0</v>
+        <v>90182.0</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Derecho</t>
-        </is>
+          <t>Programa de Doctorat en Química Teòrica i Modelització Computacional</t>
+        </is>
+      </c>
+      <c r="C98" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>90169.0</v>
+        <v>90184.0</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Economía y Empresa</t>
-        </is>
+          <t>Programa de Doctorat Europeu Conjunt Marie Sklodowska-Curie en Geoinformàtica</t>
+        </is>
+      </c>
+      <c r="C99" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>90170.0</v>
+        <v>90191.0</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Educación</t>
-        </is>
+          <t>Programa de Doctorat Europeu Conjunt Marie Sklodowska-Curie en Aplicacions dinàmiques de wearables amb estriccions de privacitat (A-WEAR)</t>
+        </is>
+      </c>
+      <c r="C100" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>90171.0</v>
+        <v>90176.0</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Estudios Interdisciplinarios de Género</t>
-        </is>
+          <t>Programa de Doctorat en Informàtica (Programa 2021)</t>
+        </is>
+      </c>
+      <c r="C101" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>90172.0</v>
+        <v>90162.0</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Estudios Internacionales en Paz, Conflictos y Desarrollo</t>
-        </is>
+          <t>Programa de Doctorat en Ciències (Programa 2021)</t>
+        </is>
+      </c>
+      <c r="C102" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>90173.0</v>
+        <v>90183.0</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Ética y Democracia</t>
-        </is>
+          <t>Programa de Doctorat en Tecnologies Industrials i Materials (Programa 2021)</t>
+        </is>
+      </c>
+      <c r="C103" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>90174.0</v>
+        <v>90168.0</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Historia del Arte</t>
-        </is>
+          <t>Programa de Doctorat en Dret (Programa 2021)</t>
+        </is>
+      </c>
+      <c r="C104" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>90175.0</v>
+        <v>90178.0</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Historia y Estudios Contemporáneos</t>
-        </is>
+          <t>Programa de Doctorat en Màrqueting (Programa 2021)</t>
+        </is>
+      </c>
+      <c r="C105" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>90176.0</v>
+        <v>90177.0</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Informática</t>
-        </is>
+          <t>Programa de Doctorat en Llengües Aplicades, Literatura i Traducció (Programa 2022)</t>
+        </is>
+      </c>
+      <c r="C106" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>90177.0</v>
+        <v>90167.0</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Lenguas Aplicadas, Literatura y Traducción</t>
-        </is>
+          <t>Programa de Doctorat en Disseny, Gestió i Avaluació de Polítiques Públiques de Benestar Social (Programa 2022)</t>
+        </is>
+      </c>
+      <c r="C107" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>90178.0</v>
+        <v>90180.0</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Márketing</t>
-        </is>
+          <t>Programa de Doctorat en Psicologia (Programa 2022)</t>
+        </is>
+      </c>
+      <c r="C108" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>90179.0</v>
+        <v>90181.0</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Nanociencia y Nanotecnología</t>
-        </is>
+          <t>Programa de Doctorat en Química Sostenible (Programa 2022)</t>
+        </is>
+      </c>
+      <c r="C109" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>90180.0</v>
+        <v>90164.0</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Psicología</t>
-        </is>
+          <t>Programa de Doctorat en Ciències de la Comunicació (programa 2022)</t>
+        </is>
+      </c>
+      <c r="C110" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>90181.0</v>
+        <v>90173.0</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Química Sostenible</t>
-        </is>
+          <t>Programa de Doctorat en Ètica i Democràcia (Programa 2023)</t>
+        </is>
+      </c>
+      <c r="C111" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>90182.0</v>
+        <v>90170.0</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Química Teórica y Modelización Computacional</t>
-        </is>
+          <t>Programa de Doctorat en Educació (Programa 2023)</t>
+        </is>
+      </c>
+      <c r="C112" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>90183.0</v>
+        <v>90175.0</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Tecnologías Industriales y Materiales</t>
-        </is>
+          <t>Programa de Doctorat en Història i Estudis Contemporanis (Programa 2024)</t>
+        </is>
+      </c>
+      <c r="C113" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>90184.0</v>
+        <v>90197.0</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Programa de Doctorado Europeo Conjunto Marie Sklodowska-Curie en Geoinformática</t>
-        </is>
+          <t>Programa de Doctorat en Història, Patrimoni i Territori</t>
+        </is>
+      </c>
+      <c r="C114" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>90185.0</v>
+        <v>90169.0</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Máster Universitario en Economía</t>
-        </is>
+          <t>Programa de Doctorat en Economia i Empresa (Programa 2024)</t>
+        </is>
+      </c>
+      <c r="C115" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>90186.0</v>
+        <v>90165.0</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Máster Universitario en Enfermería de Urgencias, Emergencias y Cuidados Críticos</t>
-        </is>
+          <t>Programa de Doctorat en Ciències de la Infermeria (Programa 2024)</t>
+        </is>
+      </c>
+      <c r="C116" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>90187.0</v>
+        <v>90172.0</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Máster Universitario Erasmus Mundus en Robótica Inteligente Marina y Marítima</t>
-        </is>
+          <t>Programa de doctorat en Estudis Internacionals en Pau, Conflictes i Desenvolupament (Programa 2025)</t>
+        </is>
+      </c>
+      <c r="C117" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>90188.0</v>
+        <v>90170.0</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Grado en Ciencias de la Actividad Física y del Deporte</t>
-        </is>
+          <t>Programa de Doctorat en Educació (Programa 2025)</t>
+        </is>
+      </c>
+      <c r="C118" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>90189.0</v>
+        <v>90164.0</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Programa de Máster Transversal en Ciencia y Tecnología</t>
-        </is>
+          <t>Doctorat en Ciències de la Comunicació (programa 2025)</t>
+        </is>
+      </c>
+      <c r="C119" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>90190.0</v>
+        <v>90175.0</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Grado en Inteligencia Robótica</t>
-        </is>
+          <t>Programa  de Doctorat en Història i Estudis Contemparanis</t>
+        </is>
+      </c>
+      <c r="C120" s="1" t="n">
+        <v>3165.0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>90191.0</v>
+        <v>90128.0</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Programa de Doctorat Europeu Conjunt Marie Sklodowska-Curie en Aplicacions dinàmiques de wearables amb estriccions de privacitat (A-WEAR)</t>
-        </is>
+          <t>Màster en Internacionalització Econòmica: Integració i Comerç Internacional</t>
+        </is>
+      </c>
+      <c r="C121" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>90192.0</v>
+        <v>90136.0</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Grado en Bioquímica y Biología Molecular</t>
-        </is>
+          <t>Màster en Màrqueting i Investigació de Mercats</t>
+        </is>
+      </c>
+      <c r="C122" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>90193.0</v>
+        <v>90118.0</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Grado en Marketing</t>
-        </is>
+          <t>Màster Internacional en Estudis de Pau, Conflictes i Desenvolupament</t>
+        </is>
+      </c>
+      <c r="C123" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>90194.0</v>
+        <v>90102.0</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Grado en Economía de la Empresa internacional / Bachelor in International Business Economics</t>
-        </is>
+          <t>Màster en Assessorament Lingüístic i Cultura Literària: Aplicacions al Context Valencià</t>
+        </is>
+      </c>
+      <c r="C124" s="1" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>90195.0</v>
+        <v>90106.0</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Máster Universitario en Gestión Administrativa</t>
-        </is>
+          <t>Màster en Ciència, Tecnologia i Aplicacions dels Materials Ceràmics</t>
+        </is>
+      </c>
+      <c r="C125" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>90196.0</v>
+        <v>90137.0</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Doble Grado en Maestro o Maestra en Educación Infantil y Primaria</t>
-        </is>
+          <t>Màster en Matemàtica Computacional</t>
+        </is>
+      </c>
+      <c r="C126" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>90197.0</v>
+        <v>90141.0</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Programa de Doctorado en Historia, Patrimonio y Territorio</t>
-        </is>
+          <t>Màster en Prevenció de Riscs Laborals</t>
+        </is>
+      </c>
+      <c r="C127" s="1" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>90198.0</v>
+        <v>90150.0</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Doble Grado en Diseño y Desarrollo de Videojuegos y Comunicación Audiovisual</t>
-        </is>
+          <t>Màster en Química Sostenible</t>
+        </is>
+      </c>
+      <c r="C128" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>90199.0</v>
+        <v>90155.0</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Doble Grado en Comunicación Audiovisual y Humanidades</t>
-        </is>
+          <t>Màster en Sistemes Intel·ligents</t>
+        </is>
+      </c>
+      <c r="C129" s="1" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
+        <v>90112.0</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Màster en Disseny i Fabricació</t>
+        </is>
+      </c>
+      <c r="C130" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>90129.0</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Màster en Intervenció i Mediació Familiar</t>
+        </is>
+      </c>
+      <c r="C131" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>90114.0</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Màster en Eficiència Energètica i Sostenibilitat en Instal·lacions Industrials i Edificació</t>
+        </is>
+      </c>
+      <c r="C132" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>90124.0</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Màster en Gestió i Promoció del Desenvolupament Local</t>
+        </is>
+      </c>
+      <c r="C133" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>90156.0</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Màster en Sostenibilitat i Responsabilitat Social Corporativa</t>
+        </is>
+      </c>
+      <c r="C134" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>90109.0</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Màster en Cooperació al Desenvolupament</t>
+        </is>
+      </c>
+      <c r="C135" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>90127.0</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Màster en Igualtat i Gènere en l'Àmbit Públic i Privat</t>
+        </is>
+      </c>
+      <c r="C136" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>90131.0</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Màster en Investigació en Atenció Primària</t>
+        </is>
+      </c>
+      <c r="C137" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>90159.0</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Màster en Tecnologies de la Traducció i Localització</t>
+        </is>
+      </c>
+      <c r="C138" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>90160.0</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Màster en Traducció Medicosanitària</t>
+        </is>
+      </c>
+      <c r="C139" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>90139.0</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Màster en Noves Tendències i Processos d'Innovació en Comunicació</t>
+        </is>
+      </c>
+      <c r="C140" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>90145.0</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Màster en Psicologia del Treball, de les Organitzacions i en Recursos Humans</t>
+        </is>
+      </c>
+      <c r="C141" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>90147.0</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Màster en Psicopatologia, Salut i Neuropsicologia</t>
+        </is>
+      </c>
+      <c r="C142" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>90122.0</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Màster en Gestió de la Qualitat</t>
+        </is>
+      </c>
+      <c r="C143" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>90157.0</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Màster en Tècniques Cromatogràfiques Aplicades</t>
+        </is>
+      </c>
+      <c r="C144" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>90138.0</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Màster en Nanociència i Nanotecnologia Molecular</t>
+        </is>
+      </c>
+      <c r="C145" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>90103.0</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Màster en Biologia Molecular, Cel·lular i Genètica</t>
+        </is>
+      </c>
+      <c r="C146" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>90158.0</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Màster en Ciència en Tecnologia Geoespacial</t>
+        </is>
+      </c>
+      <c r="C147" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>90117.0</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Màster en Estudis Contemporanis i Investigació Avançada</t>
+        </is>
+      </c>
+      <c r="C148" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>90123.0</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Màster en Gestió Financera i Comptabilitat Avançada</t>
+        </is>
+      </c>
+      <c r="C149" s="1" t="n">
+        <v>318.0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>90116.0</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Màster en Ensenyament i Adquisició de la Llengua Anglesa en Contextos Multilingües (MELACOM)</t>
+        </is>
+      </c>
+      <c r="C150" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>90151.0</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Màster Internacional en Química Teòrica i Modelatge Computacional</t>
+        </is>
+      </c>
+      <c r="C151" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>90140.0</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Màster en Pràctica Jurídica</t>
+        </is>
+      </c>
+      <c r="C152" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>90126.0</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Màster en Història i Identitats Hispàniques en el Mediterrani Occidental (segles XV-XIX)</t>
+        </is>
+      </c>
+      <c r="C153" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>90108.0</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Màster en Formació en la Comunicació Intercultural en Ensenyament de Llengües</t>
+        </is>
+      </c>
+      <c r="C154" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>90128.0</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Internacionalització Econòmica: Integració i Comerç Internacional</t>
+        </is>
+      </c>
+      <c r="C155" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>90136.0</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Màrqueting i Investigació de Mercats</t>
+        </is>
+      </c>
+      <c r="C156" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>90118.0</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Màster Universitari Internacional en Estudis de Pau, Conflictes i Desenvolupament</t>
+        </is>
+      </c>
+      <c r="C157" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>90106.0</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ciència, Tecnologia i Aplicacions dels Materials Ceràmics</t>
+        </is>
+      </c>
+      <c r="C158" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>90137.0</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Matemàtica Computacional</t>
+        </is>
+      </c>
+      <c r="C159" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>90141.0</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Prevenció de Riscos Laborals</t>
+        </is>
+      </c>
+      <c r="C160" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>90150.0</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Sostenible</t>
+        </is>
+      </c>
+      <c r="C161" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>90155.0</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Sistemes Intel·ligents</t>
+        </is>
+      </c>
+      <c r="C162" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>90112.0</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Disseny i Fabricació</t>
+        </is>
+      </c>
+      <c r="C163" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>90129.0</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Intervenció i Mediació Familiar</t>
+        </is>
+      </c>
+      <c r="C164" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>90114.0</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Eficiència Energètica i Sostenibilitat en Instal·lacions Industrials i Edificació</t>
+        </is>
+      </c>
+      <c r="C165" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>90124.0</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Gestió i Promoció del Desenvolupament Local</t>
+        </is>
+      </c>
+      <c r="C166" s="1" t="n">
+        <v>3145.0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>90156.0</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Sostenibilitat i Responsabilitat Social Corporativa</t>
+        </is>
+      </c>
+      <c r="C167" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>90109.0</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Cooperació al Desenvolupament</t>
+        </is>
+      </c>
+      <c r="C168" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>90127.0</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Igualtat i Gènere en l'Àmbit Públic i Privat</t>
+        </is>
+      </c>
+      <c r="C169" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>90131.0</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació en Atenció Primària</t>
+        </is>
+      </c>
+      <c r="C170" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>90159.0</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Tecnologies de la Traducció i Localització</t>
+        </is>
+      </c>
+      <c r="C171" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>90160.0</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Traducció Medicosanitària</t>
+        </is>
+      </c>
+      <c r="C172" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>90139.0</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Noves Tendències i Processos d'Innovació en Comunicació</t>
+        </is>
+      </c>
+      <c r="C173" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>90145.0</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans</t>
+        </is>
+      </c>
+      <c r="C174" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>90147.0</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicopatologia, Salut i Neuropsicologia</t>
+        </is>
+      </c>
+      <c r="C175" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>90122.0</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Gestió de la Qualitat</t>
+        </is>
+      </c>
+      <c r="C176" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>90157.0</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Tècniques Cromatogràfiques Aplicades</t>
+        </is>
+      </c>
+      <c r="C177" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>90138.0</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Nanociència i Nanotecnologia Molecular</t>
+        </is>
+      </c>
+      <c r="C178" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>90158.0</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Tecnologia Geoespacial/Geospatial Technologies</t>
+        </is>
+      </c>
+      <c r="C179" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>90117.0</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Estudis Contemporanis i Investigació Avançada</t>
+        </is>
+      </c>
+      <c r="C180" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>90123.0</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Gestió Financera i Comptabilitat Avançada</t>
+        </is>
+      </c>
+      <c r="C181" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>90116.0</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ensenyament i Adquisició de la Llengua Anglesa en Contextos Multilingües</t>
+        </is>
+      </c>
+      <c r="C182" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>90151.0</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Teòrica i Modelització Computacional</t>
+        </is>
+      </c>
+      <c r="C183" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>90140.0</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Pràctica Jurídica</t>
+        </is>
+      </c>
+      <c r="C184" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>90126.0</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Història i Identitats Hispàniques en el Mediterrani Occidental (segles XV-XIX)</t>
+        </is>
+      </c>
+      <c r="C185" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>90108.0</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Comunicació Intercultural i d'Ensenyament de Llengües</t>
+        </is>
+      </c>
+      <c r="C186" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>90143.0</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Professor/a d'Educació Secundària Obligatòria i Batxillerat, Formació Professional i Ensenyaments d'Idiomes</t>
+        </is>
+      </c>
+      <c r="C187" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>90119.0</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ètica i Democràcia</t>
+        </is>
+      </c>
+      <c r="C188" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>90144.0</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Protecció Integrada de Cultius</t>
+        </is>
+      </c>
+      <c r="C189" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>90103.0</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Biologia Molecular, Cel·lular i Genètica</t>
+        </is>
+      </c>
+      <c r="C190" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>90149.0</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Aplicada i Farmacològica</t>
+        </is>
+      </c>
+      <c r="C191" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>90120.0</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Física Aplicada</t>
+        </is>
+      </c>
+      <c r="C192" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>90104.0</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Catàlisi Homogènia</t>
+        </is>
+      </c>
+      <c r="C193" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>90135.0</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Llengua Anglesa per al Comerç Internacional / Master in English Language for International Trade</t>
+        </is>
+      </c>
+      <c r="C194" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>90130.0</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació Aplicada en Estudis Feministes, de Gènere i Ciutadania</t>
+        </is>
+      </c>
+      <c r="C195" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>90133.0</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació en Traducció i Interpretació</t>
+        </is>
+      </c>
+      <c r="C196" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>90125.0</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Història de l'Art i Cultura Visual</t>
+        </is>
+      </c>
+      <c r="C197" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>90154.0</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Sistema de Justícia Penal</t>
+        </is>
+      </c>
+      <c r="C198" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>90107.0</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ciències de la Infermeria</t>
+        </is>
+      </c>
+      <c r="C199" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>90109.0</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Cooperació al Desenvolupament (Pla de 2011)</t>
+        </is>
+      </c>
+      <c r="C200" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>90144.0</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Protecció Integrada de Cultius</t>
+        </is>
+      </c>
+      <c r="C201" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>90148.0</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicopedagogia</t>
+        </is>
+      </c>
+      <c r="C202" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>90152.0</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Rehabilitació Psicosocial en Salut Mental Comunitària</t>
+        </is>
+      </c>
+      <c r="C203" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>90101.0</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Advocacia</t>
+        </is>
+      </c>
+      <c r="C204" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>90142.0</v>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Procura (pendent d'autorització d'implantació)</t>
+        </is>
+      </c>
+      <c r="C205" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>90137.0</v>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Matemàtica Computacional (Pla de 2013) (Presencial)</t>
+        </is>
+      </c>
+      <c r="C206" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>90123.0</v>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Gestió Financera i Comptabilitat Avançada (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C207" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>90150.0</v>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Sostenible (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C208" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>90141.0</v>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Prevenció de Riscos Laborals (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C209" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>90106.0</v>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ciència, Tecnologia i Aplicacions dels Materials Ceràmics (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C210" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>90155.0</v>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Sistemes Intel·ligents (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C211" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>90114.0</v>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Eficiència Energètica i Sostenibilitat (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C212" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>90158.0</v>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Màster Universitari Erasmus Mundus en Tecnologia Geoespacial (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C213" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>90112.0</v>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Disseny i Fabricació (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C214" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>90157.0</v>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Tècniques Cromatogràfiques Aplicades (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C215" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>90116.0</v>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ensenyament i Adquisició de la Llengua Anglesa en Contextos Multilingües (Pla de 2013) (Presencial)</t>
+        </is>
+      </c>
+      <c r="C216" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>90139.0</v>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Noves Tendències i Processos d'Innovació en Comunicació (Pla 2013)</t>
+        </is>
+      </c>
+      <c r="C217" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>90160.0</v>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Traducció Medicosanitària (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C218" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>90108.0</v>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Comunicació Intercultural i Ensenyament de Llengües (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C219" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>90127.0</v>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Igualtat i Gènere en l'Àmbit Públic i Privat (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C220" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>90113.0</v>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Economia / Master in Economics</t>
+        </is>
+      </c>
+      <c r="C221" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>90129.0</v>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Intervenció i Mediació Familiar (Pla de 2014)</t>
+        </is>
+      </c>
+      <c r="C222" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>90145.0</v>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans (Pla de 2014) (Presencial)</t>
+        </is>
+      </c>
+      <c r="C223" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>90146.0</v>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicologia General Sanitària</t>
+        </is>
+      </c>
+      <c r="C224" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>90134.0</v>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació i Biotecnologia Agràries</t>
+        </is>
+      </c>
+      <c r="C225" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>90115.0</v>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Enginyeria Industrial</t>
+        </is>
+      </c>
+      <c r="C226" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>90118.0</v>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Estudis Internacionals de Pau, Conflictes i Desenvolupament (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C227" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>90130.0</v>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació Aplicada en Estudis Feministes, de Gènere i Ciutadania (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C228" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>90119.0</v>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ètica i Democràcia (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C229" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>90133.0</v>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació en Traducció i Interpretació (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C230" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>90107.0</v>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ciències de la Infermeria (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C231" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>90151.0</v>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Teòrica i Modelització Computacional (Pla de 2014)</t>
+        </is>
+      </c>
+      <c r="C232" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>90144.0</v>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Protecció Integrada de Cultius (Pla de 2013)</t>
+        </is>
+      </c>
+      <c r="C233" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>90126.0</v>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Història i Identitats en el Mediterrani Occidental (segles XV-XIX) (Pla de 2014)</t>
+        </is>
+      </c>
+      <c r="C234" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>90111.0</v>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Direcció d'Empreses / Master in Management</t>
+        </is>
+      </c>
+      <c r="C235" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>90112.0</v>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Disseny i Fabricació (Pla de 2015)</t>
+        </is>
+      </c>
+      <c r="C236" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>90153.0</v>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Màster Universitari Erasmus Mundus en Robòtica Avançada</t>
+        </is>
+      </c>
+      <c r="C237" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>90150.0</v>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Sostenible (Pla de 2015)</t>
+        </is>
+      </c>
+      <c r="C238" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>90132.0</v>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació en Cervell i Conducta</t>
+        </is>
+      </c>
+      <c r="C239" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>90110.0</v>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Didàctica de la Música</t>
+        </is>
+      </c>
+      <c r="C240" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>90109.0</v>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Cooperació al Desenvolupament (Pla de 2015) (Presencial)</t>
+        </is>
+      </c>
+      <c r="C241" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>90139.0</v>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Noves Tendències i Processos d'Innovació en Comunicació (Pla de 2016)</t>
+        </is>
+      </c>
+      <c r="C242" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>90130.0</v>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació Aplicada en Estudis Feministes, de Gènere i Ciutadania (Pla de 2016)</t>
+        </is>
+      </c>
+      <c r="C243" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>90156.0</v>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Sostenibilitat i Responsabilitat Social Corporativa (Pla de 2017)</t>
+        </is>
+      </c>
+      <c r="C244" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>90114.0</v>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Eficiència Energètica i Sostenibilitat (Pla de 2018)</t>
+        </is>
+      </c>
+      <c r="C245" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>90185.0</v>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Economia</t>
+        </is>
+      </c>
+      <c r="C246" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>90130.0</v>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació Aplicada en Estudis Feministes, de Gènere i Ciutadania (Pla de 2019)</t>
+        </is>
+      </c>
+      <c r="C247" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>90186.0</v>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Infermeria d'Urgències, Emergències i Cures Crítiques</t>
+        </is>
+      </c>
+      <c r="C248" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>90187.0</v>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Màster Universitari Erasmus Mundus en Robòtica Intel·ligent Marina i Marítima</t>
+        </is>
+      </c>
+      <c r="C249" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>90150.0</v>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Sostenible (Pla de 2020)</t>
+        </is>
+      </c>
+      <c r="C250" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>90158.0</v>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Tecnologia Geoespacial (Pla de 2020) / Master in Geospatial Technologies (2020 Programme of Study)</t>
+        </is>
+      </c>
+      <c r="C251" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>90132.0</v>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació en Cervell i Conducta (Pla de 2021)</t>
+        </is>
+      </c>
+      <c r="C252" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
+        <v>90151.0</v>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Teòrica i Modelització Computacional (Pla de 2021)</t>
+        </is>
+      </c>
+      <c r="C253" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" s="1" t="n">
+        <v>90111.0</v>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Direcció d'Empreses (Pla de 2022) / Master in Management (2022 Programme of Study)</t>
+        </is>
+      </c>
+      <c r="C254" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" s="1" t="n">
+        <v>90130.0</v>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació Aplicada en Estudis Feministes, de Gènere i Ciutadania (Pla de 2022)</t>
+        </is>
+      </c>
+      <c r="C255" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" s="1" t="n">
+        <v>90158.0</v>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Màster Universitari Erasmus Mundus en Tecnologia Geoespacial (Pla de 2022)</t>
+        </is>
+      </c>
+      <c r="C256" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" s="1" t="n">
+        <v>90155.0</v>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Sistemes Intel·ligents (Pla de 2023)</t>
+        </is>
+      </c>
+      <c r="C257" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" s="1" t="n">
+        <v>90101.0</v>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Advocacia i Procura</t>
+        </is>
+      </c>
+      <c r="C258" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" s="1" t="n">
+        <v>90114.0</v>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Eficiència Energètica i Sostenibilitat (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C259" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" s="1" t="n">
+        <v>90112.0</v>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Disseny i Fabricació (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C260" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" s="1" t="n">
+        <v>90187.0</v>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Màster Universitari Erasmus Mundus en Robòtica Intel·ligent Marina i Marítima (Pla de 2024)</t>
+        </is>
+      </c>
+      <c r="C261" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" s="1" t="n">
+        <v>90109.0</v>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Cooperació al Desenvolupament (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C262" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" s="1" t="n">
+        <v>90108.0</v>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Comunicació Intercultural i Ensenyament de Llengües (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C263" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" s="1" t="n">
+        <v>90116.0</v>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ensenyament i Adquisició de la Llengua Anglesa en Contextos Multilingües (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C264" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" s="1" t="n">
+        <v>90118.0</v>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Estudis Internacionals de Pau, Conflictes i Desenvolupament (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C265" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" s="1" t="n">
+        <v>90195.0</v>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Gestió Administrativa</t>
+        </is>
+      </c>
+      <c r="C266" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" s="1" t="n">
+        <v>90139.0</v>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Innovació en Comunicació (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C267" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" s="1" t="n">
+        <v>90133.0</v>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Investigació en Traducció i Interpretació (Pla de 2025) / Master in Researching Translation and Interpreting (2025 Programme of Study)</t>
+        </is>
+      </c>
+      <c r="C268" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" s="1" t="n">
+        <v>90135.0</v>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Llengua Anglesa per al Comerç Internacional (Pla de 2025) / Master in English Language for International Trade (2025 Programme of Study)</t>
+        </is>
+      </c>
+      <c r="C269" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" s="1" t="n">
+        <v>90141.0</v>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Prevenció de Riscos Laborals  (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C270" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" s="1" t="n">
+        <v>90148.0</v>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicopedagogia (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C271" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" s="1" t="n">
+        <v>90149.0</v>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Química Aplicada i Farmacològica (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C272" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" s="1" t="n">
+        <v>90152.0</v>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Rehabilitació Psicosocial en Salut Mental Comunitària (Pla de 2025)</t>
+        </is>
+      </c>
+      <c r="C273" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" s="1" t="n">
+        <v>90129.0</v>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Intervenció i Mediació Familiar (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C274" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" s="1" t="n">
+        <v>90123.0</v>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Gestió Financera i Comptabilitat Avançada (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C275" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" s="1" t="n">
+        <v>90127.0</v>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Igualtat i Gènere en l'Àmbit Públic i Privat (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C276" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="1" t="n">
+        <v>90115.0</v>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Enginyeria Industrial (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C277" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="1" t="n">
         <v>90200.0</v>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Máster Universitario en Biotecnología Aplicada a la Salud Global</t>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Biotecnologia Aplicada a la Salut Global</t>
+        </is>
+      </c>
+      <c r="C278" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="1" t="n">
+        <v>90156.0</v>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Sostenibilitat i Responsabilitat Social Corporativa (Pla de 2026)</t>
+        </is>
+      </c>
+      <c r="C279" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="1" t="n">
+        <v>90145.0</v>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans (Pla de 2025) (Presencial)</t>
+        </is>
+      </c>
+      <c r="C280" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="1" t="n">
+        <v>90137.0</v>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Matemàtica Computacional (Pla de 2013) (A distància)</t>
+        </is>
+      </c>
+      <c r="C281" s="1" t="n">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="1" t="n">
+        <v>90116.0</v>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Ensenyament i Adquisició de la Llengua Anglesa en Contextos Multilingües (Pla de 2013) (A distància)</t>
+        </is>
+      </c>
+      <c r="C282" s="1" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="1" t="n">
+        <v>90145.0</v>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans (Pla de 2014) (A distància)</t>
+        </is>
+      </c>
+      <c r="C283" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="1" t="n">
+        <v>90109.0</v>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Cooperació al Desenvolupament (Pla de 2015) (A distància)</t>
+        </is>
+      </c>
+      <c r="C284" s="1" t="n">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="1" t="n">
+        <v>90145.0</v>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Màster Universitari en Psicologia del Treball, de les Organitzacions i en Recursos Humans (Pla de 2025) (A distància))</t>
+        </is>
+      </c>
+      <c r="C285" s="1" t="n">
+        <v>2922.0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <sheetData>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>with aux as (select id,uest_id from pod_titulaciones 
+union
+select id,uest_id from pop_masters where oficial='S' 
+union
+select id, 3165 uest_id from doc_programas )
+select estudio_id "estudio", nombre "nombre", uest_id "servicio" from uji_planes p join aux on aux.id= p.tit_id</t>
         </is>
       </c>
     </row>
